--- a/Employee_Reports_wi48/Ifran Ansari Q0600.xlsx
+++ b/Employee_Reports_wi48/Ifran Ansari Q0600.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1522,11 +1522,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2353,16 +2353,16 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2411,16 +2411,16 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2440,16 +2440,16 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2573,6 +2573,35 @@
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
